--- a/SuperSmelter.xlsx
+++ b/SuperSmelter.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcgar\OneDrive\Documents\Kelp Farm HC World\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcgar\OneDrive\Documents\Super-Smelter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1247BC30-67E2-403C-8EE6-4E0C2417519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEC7E29-320C-479E-9F8E-67F3B3891EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{10021CC6-D9C0-4CEE-BC71-017883C450BE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Azalea</t>
   </si>
@@ -166,13 +166,34 @@
   </si>
   <si>
     <t>Kelp Neeeded post Tick adj.</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Req. Kelp p/s</t>
+  </si>
+  <si>
+    <t>Assuming:</t>
+  </si>
+  <si>
+    <t>Kelp is best</t>
+  </si>
+  <si>
+    <t>excess kelp is no issue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +217,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,26 +260,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -257,7 +300,102 @@
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -268,6 +406,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CD9E68-106A-4D12-BE1C-6D79D7FD6613}" name="Table1" displayName="Table1" ref="A1:D30" totalsRowShown="0" headerRowDxfId="8" tableBorderDxfId="7">
+  <autoFilter ref="A1:D30" xr:uid="{32CD9E68-106A-4D12-BE1C-6D79D7FD6613}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{920B1BF8-41BC-4829-9871-694DE1DC9F55}" name="Item" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{FC2AAD3D-0FAA-4861-89F3-E61050CD866D}" name="Burning Time" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{E8DC18C7-ED21-4B2A-A43B-800B1EFA6018}" name="Ops Per Fuel" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5DE073A4-F00D-45D7-920A-C107F3120AC1}" name="Ops Per Stack" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A93167A2-8494-439F-8345-E77EB7C0E1A9}" name="Table2" displayName="Table2" ref="F2:H16" totalsRowShown="0" tableBorderDxfId="2">
+  <autoFilter ref="F2:H16" xr:uid="{A93167A2-8494-439F-8345-E77EB7C0E1A9}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D8999686-88A1-41F7-827A-4EDAAA409D00}" name="Kelp Farm" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{A197754C-98AF-475A-884B-B0830BB91701}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{F625CCB3-BCFC-4979-BD6B-1DE72CE1FFF2}" name="Column2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,611 +753,670 @@
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E1" s="1"/>
-      <c r="G1" s="6">
+      <c r="G1">
         <v>1</v>
       </c>
-      <c r="H1" s="6">
+      <c r="H1">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="7">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="7">
         <v>0.5</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="7">
         <v>32</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="G2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="7">
         <v>5</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="7">
         <v>0.5</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="7">
         <v>32</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="7">
         <v>7.5</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="7">
         <v>0.75</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="7">
         <v>48</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="7">
         <v>9</v>
       </c>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="7">
         <v>7.5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="7">
         <v>0.75</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="7">
         <v>48</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="7">
         <v>1</v>
       </c>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="7">
         <v>10</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="7">
         <v>64</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="7">
         <f>G4/C30</f>
         <v>0.45</v>
       </c>
+      <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="7">
         <v>16</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="7">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="7">
         <v>1</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="7">
         <v>16</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="3"/>
+      <c r="F8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="7">
         <f>(1-G6)</f>
         <v>0.55000000000000004</v>
       </c>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D9" s="4">
-        <v>96</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="B9" s="7">
+        <v>15</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D9" s="7">
+        <v>96</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
-        <v>15</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D10" s="4">
-        <v>96</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
+      <c r="B10" s="7">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D10" s="7">
+        <v>96</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="7">
         <f>B30/G1</f>
         <v>200</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="10">
         <f>B30/H1</f>
         <v>12.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="4">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D11" s="4">
-        <v>96</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4"/>
+      <c r="B11" s="7">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>96</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D12" s="4">
-        <v>96</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
+      <c r="B12" s="7">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D12" s="7">
+        <v>96</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="7">
         <f>($G$4/G10)/$G$1</f>
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="7">
         <f>($G$4/H10)/$G$1</f>
         <v>0.72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4">
-        <v>15</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D13" s="4">
-        <v>96</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="B13" s="7">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D13" s="7">
+        <v>96</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
-        <v>15</v>
-      </c>
-      <c r="C14" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D14" s="4">
-        <v>96</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
+      <c r="B14" s="7">
+        <v>15</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D14" s="7">
+        <v>96</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="7">
         <f>G12/$G$8</f>
         <v>8.1818181818181804E-2</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="7">
         <f>H12/$G$8</f>
         <v>1.3090909090909089</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D15" s="4">
-        <v>96</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="B15" s="7">
+        <v>15</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D15" s="7">
+        <v>96</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="4">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D16" s="4">
-        <v>96</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
+      <c r="B16" s="7">
+        <v>15</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D16" s="7">
+        <v>96</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="10">
         <f>G14+(G14*(($G$5)/20))</f>
         <v>8.5909090909090893E-2</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="10">
         <f>H14+(H14*(($G$5)/20))</f>
         <v>1.3745454545454543</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D17" s="4">
-        <v>96</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="A17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7">
+        <v>15</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D17" s="7">
+        <v>96</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="4">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D18" s="4">
-        <v>96</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="B18" s="7">
+        <v>15</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="7">
+        <v>96</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D19" s="4">
-        <v>96</v>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="B19" s="7">
+        <v>15</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="7">
+        <v>96</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="4">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D20" s="4">
-        <v>96</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="4"/>
+      <c r="B20" s="7">
+        <v>15</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D20" s="7">
+        <v>96</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="4">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D21" s="4">
-        <v>96</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4"/>
+      <c r="B21" s="7">
+        <v>15</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D21" s="7">
+        <v>96</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="4">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D22" s="4">
-        <v>96</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="4"/>
+      <c r="B22" s="7">
+        <v>15</v>
+      </c>
+      <c r="C22" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D22" s="7">
+        <v>96</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="4">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D23" s="4">
-        <v>96</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4"/>
+      <c r="B23" s="7">
+        <v>15</v>
+      </c>
+      <c r="C23" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D23" s="7">
+        <v>96</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="4">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D24" s="4">
-        <v>96</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="4"/>
+      <c r="B24" s="7">
+        <v>15</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D24" s="7">
+        <v>96</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="4">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D25" s="4">
-        <v>96</v>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="4"/>
+      <c r="B25" s="7">
+        <v>15</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D25" s="7">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="7">
         <v>60</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="7">
         <v>6</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="7">
         <v>6</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="7">
         <v>60</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="7">
         <v>6</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="7">
         <v>6</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="7">
         <v>80</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="7">
         <v>8</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="7">
         <v>512</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="7">
         <v>120</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="7">
         <v>12</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="7">
         <v>768</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <v>200</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="9">
         <v>20</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="9">
+        <f>Table1[[#This Row],[Ops Per Fuel]]*64</f>
         <v>1280</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B5FB96-90B4-4971-83A7-65C616A2678C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2">
+        <f>'Furnace Req''s'!G16</f>
+        <v>8.5909090909090893E-2</v>
+      </c>
+      <c r="C2">
+        <f>B2*C1</f>
+        <v>1.3745454545454543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>